--- a/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Mujeres</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:57</t>
+    <t xml:space="preserve">2026-07-29 11:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -55,13 +55,19 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">Tasa de ocupación formal dependiente</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Antofagasta (Regional)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
   </si>
   <si>
     <t xml:space="preserve">Tramo de edad</t>
@@ -529,15 +535,15 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -557,7 +563,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -565,7 +571,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>35.69</v>
@@ -573,7 +579,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>59.67</v>
@@ -581,7 +587,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>53.04</v>
@@ -589,7 +595,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>14.35</v>

--- a/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:52</t>
+    <t xml:space="preserve">2026-08-19 11:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:52</t>
+    <t xml:space="preserve">2026-08-20 12:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_o_ocup_a_2018_antofagasta.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 12:16</t>
+    <t xml:space="preserve">2026-09-07 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
